--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R2" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299565</v>
+        <v>123299561</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601156</v>
+        <v>601141</v>
       </c>
       <c r="R3" t="n">
-        <v>6986026</v>
+        <v>6986053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299561</v>
+        <v>123299567</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601141</v>
+        <v>601165</v>
       </c>
       <c r="R4" t="n">
-        <v>6986053</v>
+        <v>6985987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299565</v>
+        <v>123299561</v>
       </c>
       <c r="B2" t="n">
         <v>56691</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601156</v>
+        <v>601141</v>
       </c>
       <c r="R2" t="n">
-        <v>6986026</v>
+        <v>6986053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299561</v>
+        <v>123299567</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601141</v>
+        <v>601165</v>
       </c>
       <c r="R3" t="n">
-        <v>6986053</v>
+        <v>6985987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R4" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>123299567</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299561</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R3" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299565</v>
+        <v>123299567</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601156</v>
+        <v>601165</v>
       </c>
       <c r="R4" t="n">
-        <v>6986026</v>
+        <v>6985987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299561</v>
+        <v>123299565</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601141</v>
+        <v>601156</v>
       </c>
       <c r="R2" t="n">
-        <v>6986053</v>
+        <v>6986026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299565</v>
+        <v>123299567</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601156</v>
+        <v>601165</v>
       </c>
       <c r="R3" t="n">
-        <v>6986026</v>
+        <v>6985987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299567</v>
+        <v>123299561</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601165</v>
+        <v>601141</v>
       </c>
       <c r="R4" t="n">
-        <v>6985987</v>
+        <v>6986053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299565</v>
+        <v>123299567</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601156</v>
+        <v>601165</v>
       </c>
       <c r="R2" t="n">
-        <v>6986026</v>
+        <v>6985987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R3" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R2" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299565</v>
+        <v>123299561</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601156</v>
+        <v>601141</v>
       </c>
       <c r="R3" t="n">
-        <v>6986026</v>
+        <v>6986053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299561</v>
+        <v>123299567</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601141</v>
+        <v>601165</v>
       </c>
       <c r="R4" t="n">
-        <v>6986053</v>
+        <v>6985987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299565</v>
+        <v>123299561</v>
       </c>
       <c r="B2" t="n">
         <v>56700</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601156</v>
+        <v>601141</v>
       </c>
       <c r="R2" t="n">
-        <v>6986026</v>
+        <v>6986053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299561</v>
+        <v>123299567</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601141</v>
+        <v>601165</v>
       </c>
       <c r="R3" t="n">
-        <v>6986053</v>
+        <v>6985987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299567</v>
+        <v>123299565</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601165</v>
+        <v>601156</v>
       </c>
       <c r="R4" t="n">
-        <v>6985987</v>
+        <v>6986026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299561</v>
+        <v>123299565</v>
       </c>
       <c r="B2" t="n">
         <v>56700</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601141</v>
+        <v>601156</v>
       </c>
       <c r="R2" t="n">
-        <v>6986053</v>
+        <v>6986026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299565</v>
+        <v>123299561</v>
       </c>
       <c r="B4" t="n">
         <v>56700</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601156</v>
+        <v>601141</v>
       </c>
       <c r="R4" t="n">
-        <v>6986026</v>
+        <v>6986053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18781-2023 artfynd.xlsx
+++ b/artfynd/A 18781-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123299565</v>
+        <v>123299567</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601156</v>
+        <v>601165</v>
       </c>
       <c r="R2" t="n">
-        <v>6986026</v>
+        <v>6985987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123299567</v>
+        <v>123299561</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601165</v>
+        <v>601141</v>
       </c>
       <c r="R3" t="n">
-        <v>6985987</v>
+        <v>6986053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>383</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gammal sälg</t>
+          <t>spillning, 2 stora högar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123299561</v>
+        <v>123299565</v>
       </c>
       <c r="B4" t="n">
         <v>56700</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601141</v>
+        <v>601156</v>
       </c>
       <c r="R4" t="n">
-        <v>6986053</v>
+        <v>6986026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>379</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning, 2 stora högar</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
